--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130006698</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>471040</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6538919</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130006694</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130006698</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130111912</v>
       </c>
       <c r="B4" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130111912</v>
+        <v>130322996</v>
       </c>
       <c r="B4" t="n">
-        <v>57016</v>
+        <v>5197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471044</v>
+        <v>471047</v>
       </c>
       <c r="R4" t="n">
-        <v>6538957</v>
+        <v>6538937</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,27 +974,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130322996</v>
+        <v>130111912</v>
       </c>
       <c r="B5" t="n">
-        <v>5197</v>
+        <v>57016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,39 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471047</v>
+        <v>471044</v>
       </c>
       <c r="R5" t="n">
-        <v>6538937</v>
+        <v>6538957</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1091,27 +1091,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>130111912</v>
       </c>
       <c r="B5" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>130111912</v>
       </c>
       <c r="B5" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>130111912</v>
       </c>
       <c r="B5" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>130111912</v>
       </c>
       <c r="B5" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>130006694</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -795,11 +795,11 @@
         <v>130006698</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130322996</v>
+        <v>130111912</v>
       </c>
       <c r="B4" t="n">
-        <v>5197</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471047</v>
+        <v>471044</v>
       </c>
       <c r="R4" t="n">
-        <v>6538937</v>
+        <v>6538957</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,27 +974,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130111912</v>
+        <v>130322807</v>
       </c>
       <c r="B5" t="n">
-        <v>57073</v>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,39 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471044</v>
+        <v>471012</v>
       </c>
       <c r="R5" t="n">
-        <v>6538957</v>
+        <v>6538879</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1091,27 +1091,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,6 +1135,240 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130323210</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Boramossen, Boramossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>471119</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6538921</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130322996</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>471047</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6538937</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130322807</v>
+        <v>130323049</v>
       </c>
       <c r="B5" t="n">
-        <v>5179</v>
+        <v>4776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471012</v>
+        <v>471059</v>
       </c>
       <c r="R5" t="n">
-        <v>6538879</v>
+        <v>6538942</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>Äldre gnag och kläckhål på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130323210</v>
+        <v>130323305</v>
       </c>
       <c r="B6" t="n">
-        <v>5179</v>
+        <v>4776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,14 +1174,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471119</v>
+        <v>471104</v>
       </c>
       <c r="R6" t="n">
-        <v>6538921</v>
+        <v>6538899</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130322996</v>
+        <v>130322807</v>
       </c>
       <c r="B7" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471047</v>
+        <v>471012</v>
       </c>
       <c r="R7" t="n">
-        <v>6538937</v>
+        <v>6538879</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1369,6 +1369,240 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130323210</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Boramossen, Boramossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>471119</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6538921</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130322996</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>471047</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6538937</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56017-2025 artfynd.xlsx
+++ b/artfynd/A 56017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130006694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130006698</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111912</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323049</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323305</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322807</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323210</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1603,8 +1643,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322996</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>